--- a/grupos/6ARHM - Estadisticos 20212.xlsx
+++ b/grupos/6ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -149,18 +149,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -179,30 +179,69 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
@@ -212,15 +251,9 @@
     <t>PARRA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>TREJO</t>
   </si>
   <si>
@@ -233,9 +266,6 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>WILSON</t>
   </si>
   <si>
@@ -245,9 +275,6 @@
     <t>OLTEHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -260,15 +287,9 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -278,12 +299,6 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
     <t>HANNIA MONSERRAT</t>
   </si>
   <si>
@@ -296,9 +311,6 @@
     <t>XIMENA</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
     <t>FERNANDA CAMILA</t>
   </si>
   <si>
@@ -308,9 +320,6 @@
     <t>MELISSA MONSERRAT</t>
   </si>
   <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
     <t>ITZEL</t>
   </si>
   <si>
@@ -320,18 +329,12 @@
     <t>ALMA EDITH</t>
   </si>
   <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
     <t>KATHE ALONDRA</t>
   </si>
   <si>
     <t>MARLENE ALICIA</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>MARISOL</t>
   </si>
   <si>
@@ -342,9 +345,6 @@
   </si>
   <si>
     <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
 </sst>
 </file>
@@ -836,13 +836,13 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -890,13 +890,13 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -913,13 +913,13 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -967,13 +967,13 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -990,13 +990,13 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1044,13 +1044,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1067,13 +1067,13 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>9</v>
@@ -1121,13 +1121,13 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1144,13 +1144,13 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>9</v>
@@ -1198,13 +1198,13 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1221,13 +1221,13 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1275,13 +1275,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1298,13 +1298,13 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1352,13 +1352,13 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1375,13 +1375,13 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1429,13 +1429,13 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1452,13 +1452,13 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>7</v>
@@ -1506,13 +1506,13 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1529,13 +1529,13 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1583,13 +1583,13 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1606,13 +1606,13 @@
         <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1660,13 +1660,13 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1683,13 +1683,13 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1737,13 +1737,13 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1760,13 +1760,13 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -1814,13 +1814,13 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1837,13 +1837,13 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>9</v>
@@ -1891,13 +1891,13 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1914,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -1968,13 +1968,13 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1991,13 +1991,13 @@
         <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>9</v>
@@ -2045,13 +2045,13 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2068,13 +2068,13 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>-1</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2145,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>9</v>
@@ -2199,13 +2199,13 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2222,13 +2222,13 @@
         <v>10</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>10</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -2276,13 +2276,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -2353,13 +2353,13 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2376,13 +2376,13 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>9</v>
@@ -2430,13 +2430,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2453,13 +2453,13 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2581,109 +2581,115 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
       <c r="I2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>22</v>
       </c>
       <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="G3">
+        <v>18.18</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>22</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>72.73</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>27.27</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>22</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>81.81999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="G5">
-        <v>18.18</v>
+        <v>4.55</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2694,7 +2700,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2703,25 +2709,25 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>95.45</v>
+      </c>
+      <c r="G6">
+        <v>4.55</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>90.91</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>9.09</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2763,7 +2769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2798,16 +2804,16 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2818,13 +2824,13 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -2832,59 +2838,59 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920125</v>
+        <v>19330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920125</v>
+        <v>19330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920126</v>
+        <v>19330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -2892,39 +2898,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920126</v>
+        <v>19330051920139</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920127</v>
+        <v>19330051920139</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
@@ -2932,902 +2938,22 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920127</v>
+        <v>19330051920431</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920128</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920128</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920129</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920129</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920130</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920380</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920380</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920131</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920131</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920132</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920132</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920133</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920133</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920133</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920134</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920135</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920135</v>
-      </c>
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920002</v>
-      </c>
-      <c r="B30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920002</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920136</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920136</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920136</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920137</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920137</v>
-      </c>
-      <c r="B36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920140</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920140</v>
-      </c>
-      <c r="B38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920139</v>
-      </c>
-      <c r="B39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920139</v>
-      </c>
-      <c r="B40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920139</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920139</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920143</v>
-      </c>
-      <c r="B43" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920143</v>
-      </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920141</v>
-      </c>
-      <c r="B45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920141</v>
-      </c>
-      <c r="B46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920144</v>
-      </c>
-      <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" t="s">
-        <v>106</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920144</v>
-      </c>
-      <c r="B48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920147</v>
-      </c>
-      <c r="B49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920147</v>
-      </c>
-      <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920431</v>
-      </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920431</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" t="s">
-        <v>108</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920431</v>
-      </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" t="s">
-        <v>108</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3869,13 +2995,13 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3883,16 +3009,16 @@
         <v>19330051920139</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3900,16 +3026,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3917,16 +3043,16 @@
         <v>19330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3934,16 +3060,16 @@
         <v>19330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3951,16 +3077,16 @@
         <v>19330051920431</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3968,16 +3094,16 @@
         <v>19330051920126</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3985,16 +3111,16 @@
         <v>19330051920127</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4002,16 +3128,16 @@
         <v>19330051920128</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4019,16 +3145,16 @@
         <v>19330051920129</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4036,16 +3162,16 @@
         <v>19330051920380</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4053,16 +3179,16 @@
         <v>19330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4070,16 +3196,16 @@
         <v>19330051920132</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4087,16 +3213,16 @@
         <v>19330051920134</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4104,16 +3230,16 @@
         <v>19330051920135</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4121,16 +3247,16 @@
         <v>19330051920002</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4138,16 +3264,16 @@
         <v>19330051920137</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4155,16 +3281,16 @@
         <v>19330051920140</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4172,16 +3298,16 @@
         <v>19330051920143</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4189,16 +3315,16 @@
         <v>19330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4206,16 +3332,16 @@
         <v>19330051920144</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4223,16 +3349,16 @@
         <v>19330051920147</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4242,7 +3368,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4274,19 +3400,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920126</v>
+        <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>43</v>
@@ -4297,42 +3423,42 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920126</v>
+        <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920127</v>
+        <v>19330051920133</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -4343,42 +3469,42 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920127</v>
+        <v>19330051920133</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920128</v>
+        <v>19330051920136</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -4389,622 +3515,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920128</v>
+        <v>19330051920431</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920129</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920129</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920380</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920380</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920131</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920132</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920132</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920134</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920135</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920135</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920002</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920002</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920137</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920137</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920140</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920140</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920143</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920143</v>
-      </c>
-      <c r="B27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920141</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920141</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920144</v>
-      </c>
-      <c r="B30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920144</v>
-      </c>
-      <c r="B31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920147</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330051920147</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20212.xlsx
+++ b/grupos/6ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -149,12 +149,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -179,172 +179,172 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SOLIS</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>YATZIRI NAOMI</t>
+    <t>HANNIA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ISMERAI</t>
+  </si>
+  <si>
+    <t>DAMARIS JABNEL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
+    <t>FERNANDA CAMILA</t>
+  </si>
+  <si>
+    <t>NURIEL</t>
+  </si>
+  <si>
+    <t>MELISSA MONSERRAT</t>
+  </si>
+  <si>
     <t>DENISSE MERARY</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CATHERIN DALAY</t>
+  </si>
+  <si>
+    <t>ALMA EDITH</t>
+  </si>
+  <si>
     <t>ROCIO</t>
   </si>
   <si>
-    <t>DANIELA</t>
+    <t>KATHE ALONDRA</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>CRISTINA</t>
+  </si>
+  <si>
+    <t>RENATA</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
   <si>
     <t>ARACELY</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HANNIA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISMERAI</t>
-  </si>
-  <si>
-    <t>DAMARIS JABNEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>FERNANDA CAMILA</t>
-  </si>
-  <si>
-    <t>NURIEL</t>
-  </si>
-  <si>
-    <t>MELISSA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CATHERIN DALAY</t>
-  </si>
-  <si>
-    <t>ALMA EDITH</t>
-  </si>
-  <si>
-    <t>KATHE ALONDRA</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>CRISTINA</t>
-  </si>
-  <si>
-    <t>RENATA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -830,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -884,7 +884,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1215,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1523,7 +1523,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1831,7 +1831,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1923,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -1977,7 +1977,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2062,7 +2062,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2447,7 +2447,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2581,30 +2581,30 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2625,7 +2625,7 @@
         <v>18.18</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2769,7 +2769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2804,10 +2804,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2818,142 +2818,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920125</v>
+        <v>19330051920139</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920133</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920136</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920139</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920431</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2995,13 +2875,13 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3009,95 +2889,95 @@
         <v>19330051920139</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920130</v>
+        <v>19330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920133</v>
+        <v>19330051920127</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920136</v>
+        <v>19330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920431</v>
+        <v>19330051920129</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920126</v>
+        <v>19330051920130</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -3108,13 +2988,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920127</v>
+        <v>19330051920380</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -3125,13 +3005,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920128</v>
+        <v>19330051920131</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>95</v>
@@ -3142,13 +3022,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920129</v>
+        <v>19330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>96</v>
@@ -3159,13 +3039,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920380</v>
+        <v>19330051920133</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>97</v>
@@ -3176,13 +3056,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920131</v>
+        <v>19330051920134</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
@@ -3193,13 +3073,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920132</v>
+        <v>19330051920135</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3210,13 +3090,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920134</v>
+        <v>19330051920002</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3227,13 +3107,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920135</v>
+        <v>19330051920136</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -3244,13 +3124,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920002</v>
+        <v>19330051920137</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
         <v>102</v>
@@ -3261,13 +3141,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920137</v>
+        <v>19330051920140</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -3278,13 +3158,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920140</v>
+        <v>19330051920143</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>104</v>
@@ -3295,13 +3175,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920143</v>
+        <v>19330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -3312,13 +3192,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920141</v>
+        <v>19330051920144</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3329,13 +3209,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920144</v>
+        <v>19330051920147</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3346,13 +3226,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920147</v>
+        <v>19330051920431</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>108</v>
@@ -3368,7 +3248,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3403,22 +3283,22 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3426,19 +3306,19 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3449,91 +3329,45 @@
         <v>19330051920133</v>
       </c>
       <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
         <v>54</v>
       </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920133</v>
+        <v>19330051920431</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
       </c>
       <c r="G5">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920136</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920431</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHM - Estadisticos 20212.xlsx
+++ b/grupos/6ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -848,22 +848,22 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -884,7 +884,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -925,22 +925,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -961,7 +961,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1002,22 +1002,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1038,19 +1038,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1079,22 +1079,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1115,10 +1115,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1156,22 +1156,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1192,10 +1192,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1204,10 +1204,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1233,22 +1233,22 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1275,13 +1275,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1313,19 +1313,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1387,22 +1387,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1467,19 +1467,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1544,19 +1544,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1586,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1618,22 +1618,22 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1654,19 +1654,19 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1698,19 +1698,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1772,22 +1772,22 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1808,22 +1808,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1849,22 +1849,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1885,19 +1885,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1926,22 +1926,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1962,19 +1962,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2003,22 +2003,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2039,19 +2039,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2080,22 +2080,22 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2160,19 +2160,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2202,13 +2202,13 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2234,22 +2234,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2311,22 +2311,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2347,19 +2347,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2388,22 +2388,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2468,19 +2468,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2504,19 +2504,19 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2581,19 +2581,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>81.81999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="G2">
-        <v>18.18</v>
+        <v>22.73</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>18.18</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -2689,7 +2689,7 @@
         <v>4.55</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>4.55</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3248,7 +3248,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3280,39 +3280,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920130</v>
+        <v>19330051920125</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920130</v>
+        <v>19330051920125</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920133</v>
+        <v>19330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3349,24 +3349,116 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
+        <v>19330051920130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>19330051920431</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>88</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>108</v>
       </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
         <v>44</v>
       </c>
-      <c r="G5">
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20212.xlsx
+++ b/grupos/6ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -149,16 +149,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
@@ -869,7 +869,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -881,13 +881,13 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>6</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -899,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -946,7 +946,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -958,7 +958,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1035,7 +1035,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1112,7 +1112,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1177,7 +1177,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1254,7 +1254,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1284,7 +1284,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1331,7 +1331,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1408,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1420,13 +1420,13 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1485,7 +1485,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1497,13 +1497,13 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1562,7 +1562,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1574,13 +1574,13 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1592,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1639,7 +1639,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1651,13 +1651,13 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1793,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1805,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1870,7 +1870,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1882,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1947,7 +1947,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2101,7 +2101,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2113,13 +2113,13 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2131,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2178,7 +2178,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2255,7 +2255,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2332,7 +2332,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2344,13 +2344,13 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2409,7 +2409,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2486,7 +2486,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2498,25 +2498,25 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>5</v>
       </c>
       <c r="U25">
+        <v>8</v>
+      </c>
+      <c r="V25">
+        <v>10</v>
+      </c>
+      <c r="W25">
+        <v>9</v>
+      </c>
+      <c r="X25">
+        <v>10</v>
+      </c>
+      <c r="Y25">
         <v>7</v>
-      </c>
-      <c r="V25">
-        <v>10</v>
-      </c>
-      <c r="W25">
-        <v>9</v>
-      </c>
-      <c r="X25">
-        <v>10</v>
-      </c>
-      <c r="Y25">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2581,19 +2581,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G2">
-        <v>22.73</v>
+        <v>18.18</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2613,30 +2613,30 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="G3">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -2645,33 +2645,33 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>22</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2709,19 +2709,19 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2833,7 +2833,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3248,7 +3248,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3295,7 +3295,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -3303,19 +3303,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920125</v>
+        <v>19330051920129</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -3341,7 +3341,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3349,116 +3349,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920130</v>
+        <v>19330051920431</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920431</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920431</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920129</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920133</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20212.xlsx
+++ b/grupos/6ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -149,21 +149,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -179,157 +179,157 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>YATZIRI NAOMI</t>
   </si>
   <si>
+    <t>HANNIA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ISMERAI</t>
+  </si>
+  <si>
+    <t>DAMARIS JABNEL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FERNANDA CAMILA</t>
+  </si>
+  <si>
+    <t>NURIEL</t>
+  </si>
+  <si>
+    <t>MELISSA MONSERRAT</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CATHERIN DALAY</t>
+  </si>
+  <si>
+    <t>ALMA EDITH</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>KATHE ALONDRA</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>HANNIA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISMERAI</t>
-  </si>
-  <si>
-    <t>DAMARIS JABNEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FERNANDA CAMILA</t>
-  </si>
-  <si>
-    <t>NURIEL</t>
-  </si>
-  <si>
-    <t>MELISSA MONSERRAT</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CATHERIN DALAY</t>
-  </si>
-  <si>
-    <t>ALMA EDITH</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
-    <t>KATHE ALONDRA</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
   </si>
   <si>
     <t>MARISOL</t>
@@ -839,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -857,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -866,19 +866,19 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -890,13 +890,13 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -943,19 +943,19 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1020,19 +1020,19 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -1097,19 +1097,19 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1174,25 +1174,25 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>8</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1204,7 +1204,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1251,37 +1251,37 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>8</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1310,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -1328,25 +1328,25 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1405,25 +1405,25 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1464,7 +1464,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1482,25 +1482,25 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>7</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1541,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1559,19 +1559,19 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1583,13 +1583,13 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1636,19 +1636,19 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -1713,25 +1713,25 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1790,19 +1790,19 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1867,19 +1867,19 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -1944,25 +1944,25 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2021,19 +2021,19 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2089,7 +2089,7 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2098,37 +2098,37 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>7</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2157,7 +2157,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2175,25 +2175,25 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>9</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2252,19 +2252,19 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2329,19 +2329,19 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2406,19 +2406,19 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2465,7 +2465,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -2483,25 +2483,25 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2581,19 +2581,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2604,60 +2604,60 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>22</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2677,19 +2677,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2769,7 +2769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2794,46 +2794,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920139</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2875,41 +2835,41 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920139</v>
+        <v>19330051920126</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920126</v>
+        <v>19330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>89</v>
@@ -2920,13 +2880,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920127</v>
+        <v>19330051920128</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -2937,13 +2897,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920128</v>
+        <v>19330051920129</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
@@ -2954,13 +2914,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920129</v>
+        <v>19330051920130</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
         <v>92</v>
@@ -2971,13 +2931,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920130</v>
+        <v>19330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -2988,13 +2948,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920380</v>
+        <v>19330051920131</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -3005,13 +2965,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920131</v>
+        <v>19330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
         <v>95</v>
@@ -3022,13 +2982,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920132</v>
+        <v>19330051920133</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>96</v>
@@ -3039,13 +2999,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920133</v>
+        <v>19330051920134</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
         <v>97</v>
@@ -3056,13 +3016,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920134</v>
+        <v>19330051920135</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
@@ -3073,13 +3033,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920135</v>
+        <v>19330051920002</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3090,13 +3050,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920002</v>
+        <v>19330051920136</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3107,13 +3067,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920136</v>
+        <v>19330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -3124,13 +3084,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920137</v>
+        <v>19330051920140</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>102</v>
@@ -3141,13 +3101,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920140</v>
+        <v>19330051920139</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -3161,10 +3121,10 @@
         <v>19330051920143</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>104</v>
@@ -3178,10 +3138,10 @@
         <v>19330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -3195,10 +3155,10 @@
         <v>19330051920144</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3212,10 +3172,10 @@
         <v>19330051920147</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3229,10 +3189,10 @@
         <v>19330051920431</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
         <v>108</v>
@@ -3248,7 +3208,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3278,98 +3238,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920431</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
